--- a/data/raw/2026/1-6月/酒店.xlsx
+++ b/data/raw/2026/1-6月/酒店.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA103"/>
+  <dimension ref="A1:CA115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28156,7 +28156,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>284</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -28296,12 +28296,12 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AE88" t="inlineStr">
@@ -28421,12 +28421,12 @@
       </c>
       <c r="BN88" t="inlineStr">
         <is>
-          <t>2026-06-22 12:15:24</t>
+          <t>2026-06-30 18:48:26</t>
         </is>
       </c>
       <c r="BO88" t="inlineStr">
         <is>
-          <t>2026-06-22 12:15:24</t>
+          <t>2026-06-30 18:48:26</t>
         </is>
       </c>
       <c r="BP88" t="inlineStr">
@@ -28436,7 +28436,7 @@
       </c>
       <c r="BQ88" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体AT天地(3号门)杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BR88" t="inlineStr">
@@ -28456,17 +28456,17 @@
       </c>
       <c r="BU88" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/ca9cf170544e47eeb7d7e898a46017d0.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/7cc304d643b9427e9cfc2e0e16f52e13.mp3</t>
         </is>
       </c>
       <c r="BV88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 56 秒 </t>
+          <t xml:space="preserve">2 分 53 秒 </t>
         </is>
       </c>
       <c r="BW88" t="inlineStr">
         <is>
-          <t>2026-06-22 12:12:26</t>
+          <t>2026-06-30 18:45:30</t>
         </is>
       </c>
       <c r="BX88" t="inlineStr">
@@ -28493,7 +28493,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>283</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -28513,12 +28513,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>46-55岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -28633,12 +28633,12 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AD89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AE89" t="inlineStr">
@@ -28673,22 +28673,22 @@
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -28758,12 +28758,12 @@
       </c>
       <c r="BN89" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51:53</t>
+          <t>2026-06-30 18:44:50</t>
         </is>
       </c>
       <c r="BO89" t="inlineStr">
         <is>
-          <t>2026-06-11 10:51:53</t>
+          <t>2026-06-30 18:44:50</t>
         </is>
       </c>
       <c r="BP89" t="inlineStr">
@@ -28773,7 +28773,7 @@
       </c>
       <c r="BQ89" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道滨盛路万象世界中心</t>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体AT天地(3号门)杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BR89" t="inlineStr">
@@ -28793,17 +28793,17 @@
       </c>
       <c r="BU89" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/31db1e02827040b5a6127c3c3c7a0048.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/7504544dbb3347cfb4b8c3477c66c626.mp3</t>
         </is>
       </c>
       <c r="BV89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 56 秒 </t>
+          <t xml:space="preserve">2 分 5 秒 </t>
         </is>
       </c>
       <c r="BW89" t="inlineStr">
         <is>
-          <t>2026-06-11 10:48:54</t>
+          <t>2026-06-30 18:42:42</t>
         </is>
       </c>
       <c r="BX89" t="inlineStr">
@@ -28830,7 +28830,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>282</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -28850,7 +28850,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -28860,27 +28860,27 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -28890,7 +28890,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -28970,12 +28970,12 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AE90" t="inlineStr">
@@ -29010,22 +29010,22 @@
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AL90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -29095,12 +29095,12 @@
       </c>
       <c r="BN90" t="inlineStr">
         <is>
-          <t>2026-06-09 13:18:18</t>
+          <t>2026-06-30 16:51:19</t>
         </is>
       </c>
       <c r="BO90" t="inlineStr">
         <is>
-          <t>2026-06-09 13:18:18</t>
+          <t>2026-06-30 16:51:19</t>
         </is>
       </c>
       <c r="BP90" t="inlineStr">
@@ -29130,17 +29130,17 @@
       </c>
       <c r="BU90" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/c848f3130ffa4aa7b70c43559a8851a1.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/3289db68c8b540af997196e3c6e2f9c6.mp3</t>
         </is>
       </c>
       <c r="BV90" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 分 16 秒 </t>
+          <t xml:space="preserve">3 分 3 秒 </t>
         </is>
       </c>
       <c r="BW90" t="inlineStr">
         <is>
-          <t>2026-06-09 13:14:59</t>
+          <t>2026-06-30 16:48:14</t>
         </is>
       </c>
       <c r="BX90" t="inlineStr">
@@ -29167,7 +29167,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -29177,7 +29177,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>住宿团队</t>
+          <t>散客</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -29187,12 +29187,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -29307,12 +29307,12 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AD91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AE91" t="inlineStr">
@@ -29347,22 +29347,22 @@
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -29417,7 +29417,7 @@
       </c>
       <c r="BG91" t="inlineStr">
         <is>
-          <t>达到预期</t>
+          <t>超出预期</t>
         </is>
       </c>
       <c r="BH91" t="inlineStr">
@@ -29432,12 +29432,12 @@
       </c>
       <c r="BN91" t="inlineStr">
         <is>
-          <t>2026-06-09 13:01:20</t>
+          <t>2026-06-30 16:42:39</t>
         </is>
       </c>
       <c r="BO91" t="inlineStr">
         <is>
-          <t>2026-06-09 13:01:20</t>
+          <t>2026-06-30 16:42:39</t>
         </is>
       </c>
       <c r="BP91" t="inlineStr">
@@ -29447,7 +29447,7 @@
       </c>
       <c r="BQ91" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体博览城</t>
         </is>
       </c>
       <c r="BR91" t="inlineStr">
@@ -29467,17 +29467,17 @@
       </c>
       <c r="BU91" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/1337bdfe227749f48c0a36b44f66aaf5.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/76c847d6bcca4d02bd9fdecc4ac57719.mp3</t>
         </is>
       </c>
       <c r="BV91" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 分 3 秒 </t>
+          <t xml:space="preserve">3 分 1 秒 </t>
         </is>
       </c>
       <c r="BW91" t="inlineStr">
         <is>
-          <t>2026-06-09 12:58:14</t>
+          <t>2026-06-30 16:39:35</t>
         </is>
       </c>
       <c r="BX91" t="inlineStr">
@@ -29504,7 +29504,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>280</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -29514,7 +29514,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>住宿团队</t>
+          <t>散客</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -29544,12 +29544,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -29564,7 +29564,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -29579,7 +29579,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -29594,164 +29594,164 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AN92" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AV92" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BE92" t="inlineStr">
+        <is>
+          <t>比较满意</t>
+        </is>
+      </c>
+      <c r="BF92" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AD92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AE92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AF92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AG92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AL92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="AP92" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="AQ92" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr">
-        <is>
-          <t>不知道</t>
-        </is>
-      </c>
-      <c r="AV92" t="inlineStr">
-        <is>
-          <t>不知道</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr">
-        <is>
-          <t>不知道</t>
-        </is>
-      </c>
-      <c r="BB92" t="inlineStr">
-        <is>
-          <t>不知道</t>
-        </is>
-      </c>
-      <c r="BE92" t="inlineStr">
-        <is>
-          <t>比较满意</t>
-        </is>
-      </c>
-      <c r="BF92" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="BG92" t="inlineStr">
         <is>
           <t>达到预期</t>
@@ -29767,14 +29767,19 @@
           <t>会推荐</t>
         </is>
       </c>
+      <c r="BJ92" t="inlineStr">
+        <is>
+          <t>地下车库找上去的电梯不好找</t>
+        </is>
+      </c>
       <c r="BN92" t="inlineStr">
         <is>
-          <t>2026-06-09 12:30:56</t>
+          <t>2026-06-30 16:01:05</t>
         </is>
       </c>
       <c r="BO92" t="inlineStr">
         <is>
-          <t>2026-06-09 12:30:56</t>
+          <t>2026-06-30 16:01:05</t>
         </is>
       </c>
       <c r="BP92" t="inlineStr">
@@ -29784,7 +29789,7 @@
       </c>
       <c r="BQ92" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BR92" t="inlineStr">
@@ -29804,17 +29809,17 @@
       </c>
       <c r="BU92" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/206b60b4daf54388840bd2a6c7a75e1a.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/d0a0b113a3a8414dba9ae407e93b450a.mp3</t>
         </is>
       </c>
       <c r="BV92" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 分 28 秒 </t>
+          <t xml:space="preserve">2 分 25 秒 </t>
         </is>
       </c>
       <c r="BW92" t="inlineStr">
         <is>
-          <t>2026-06-09 12:27:25</t>
+          <t>2026-06-30 15:58:38</t>
         </is>
       </c>
       <c r="BX92" t="inlineStr">
@@ -29841,7 +29846,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>279</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -29971,22 +29976,22 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AE93" t="inlineStr">
@@ -30021,22 +30026,22 @@
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AL93" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -30106,12 +30111,12 @@
       </c>
       <c r="BN93" t="inlineStr">
         <is>
-          <t>2026-06-09 11:44:30</t>
+          <t>2026-06-26 17:19:41</t>
         </is>
       </c>
       <c r="BO93" t="inlineStr">
         <is>
-          <t>2026-06-09 11:44:30</t>
+          <t>2026-06-26 17:19:41</t>
         </is>
       </c>
       <c r="BP93" t="inlineStr">
@@ -30121,7 +30126,7 @@
       </c>
       <c r="BQ93" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BR93" t="inlineStr">
@@ -30141,17 +30146,17 @@
       </c>
       <c r="BU93" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/af0b874dfb9f4f40acee55aaeffa001c.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/ec58b8eb18b845208e4e48bf3fe2dfa0.mp3</t>
         </is>
       </c>
       <c r="BV93" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 分 24 秒 </t>
+          <t xml:space="preserve">2 分 47 秒 </t>
         </is>
       </c>
       <c r="BW93" t="inlineStr">
         <is>
-          <t>2026-06-09 11:41:03</t>
+          <t>2026-06-26 17:16:50</t>
         </is>
       </c>
       <c r="BX93" t="inlineStr">
@@ -30178,7 +30183,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>278</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -30203,7 +30208,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>26-35岁</t>
+          <t>36-45岁</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -30318,12 +30323,12 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AD94" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AE94" t="inlineStr">
@@ -30358,22 +30363,22 @@
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AL94" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -30443,12 +30448,12 @@
       </c>
       <c r="BN94" t="inlineStr">
         <is>
-          <t>2026-06-09 11:12:30</t>
+          <t>2026-06-26 16:55:17</t>
         </is>
       </c>
       <c r="BO94" t="inlineStr">
         <is>
-          <t>2026-06-09 11:12:30</t>
+          <t>2026-06-26 16:55:17</t>
         </is>
       </c>
       <c r="BP94" t="inlineStr">
@@ -30478,17 +30483,17 @@
       </c>
       <c r="BU94" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/539f67c7394847f38e4ed7a904bbd915.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/c34e29424ec14a0695a9af2a703a423a.mp3</t>
         </is>
       </c>
       <c r="BV94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 22 秒 </t>
+          <t xml:space="preserve">4 分 2 秒 </t>
         </is>
       </c>
       <c r="BW94" t="inlineStr">
         <is>
-          <t>2026-06-09 11:10:05</t>
+          <t>2026-06-26 16:51:12</t>
         </is>
       </c>
       <c r="BX94" t="inlineStr">
@@ -30515,7 +30520,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>277</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -30535,12 +30540,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>26-35岁</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -30645,12 +30650,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
@@ -30695,22 +30700,22 @@
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AL95" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -30780,12 +30785,12 @@
       </c>
       <c r="BN95" t="inlineStr">
         <is>
-          <t>2026-06-09 11:03:03</t>
+          <t>2026-06-26 13:56:50</t>
         </is>
       </c>
       <c r="BO95" t="inlineStr">
         <is>
-          <t>2026-06-09 11:03:03</t>
+          <t>2026-06-26 13:56:50</t>
         </is>
       </c>
       <c r="BP95" t="inlineStr">
@@ -30795,7 +30800,7 @@
       </c>
       <c r="BQ95" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道Pet haven哈文宠物生活馆杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BR95" t="inlineStr">
@@ -30815,17 +30820,17 @@
       </c>
       <c r="BU95" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/1635becd5ed443398dea66d96928f274.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/7af6c6a8dbf54e8aa277d5bdfd2b39b9.mp3</t>
         </is>
       </c>
       <c r="BV95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 9 秒 </t>
+          <t xml:space="preserve">2 分 43 秒 </t>
         </is>
       </c>
       <c r="BW95" t="inlineStr">
         <is>
-          <t>2026-06-09 11:00:51</t>
+          <t>2026-06-26 13:54:05</t>
         </is>
       </c>
       <c r="BX95" t="inlineStr">
@@ -30852,7 +30857,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>276</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -30892,12 +30897,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -31032,22 +31037,22 @@
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -31117,12 +31122,12 @@
       </c>
       <c r="BN96" t="inlineStr">
         <is>
-          <t>2026-06-09 10:55:08</t>
+          <t>2026-06-26 13:40:21</t>
         </is>
       </c>
       <c r="BO96" t="inlineStr">
         <is>
-          <t>2026-06-09 10:55:08</t>
+          <t>2026-06-26 13:40:21</t>
         </is>
       </c>
       <c r="BP96" t="inlineStr">
@@ -31152,17 +31157,17 @@
       </c>
       <c r="BU96" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/a4dd0b1c286a42f9ada06a7fc39b2920.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/118be2c5d2994d53abbb256afa496b27.mp3</t>
         </is>
       </c>
       <c r="BV96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 分 58 秒 </t>
+          <t xml:space="preserve">2 分 1 秒 </t>
         </is>
       </c>
       <c r="BW96" t="inlineStr">
         <is>
-          <t>2026-06-09 10:53:07</t>
+          <t>2026-06-26 13:38:17</t>
         </is>
       </c>
       <c r="BX96" t="inlineStr">
@@ -31189,7 +31194,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>275</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -31209,12 +31214,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>46-55岁</t>
+          <t>36-45岁</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -31239,7 +31244,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -31319,12 +31324,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
@@ -31369,22 +31374,22 @@
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -31454,12 +31459,12 @@
       </c>
       <c r="BN97" t="inlineStr">
         <is>
-          <t>2026-06-08 18:30:21</t>
+          <t>2026-06-26 13:07:47</t>
         </is>
       </c>
       <c r="BO97" t="inlineStr">
         <is>
-          <t>2026-06-08 18:30:21</t>
+          <t>2026-06-26 13:07:47</t>
         </is>
       </c>
       <c r="BP97" t="inlineStr">
@@ -31469,7 +31474,7 @@
       </c>
       <c r="BQ97" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道XDS喜德盛自行车(杭州形象店)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BR97" t="inlineStr">
@@ -31489,17 +31494,17 @@
       </c>
       <c r="BU97" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/fc77f000748948e2b27937bcfb5dd8fa.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/34e3979b05bc416fb9056bd3ea48f8d2.mp3</t>
         </is>
       </c>
       <c r="BV97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 2 秒 </t>
+          <t xml:space="preserve">2 分 1 秒 </t>
         </is>
       </c>
       <c r="BW97" t="inlineStr">
         <is>
-          <t>2026-06-08 18:28:17</t>
+          <t>2026-06-26 13:05:43</t>
         </is>
       </c>
       <c r="BX97" t="inlineStr">
@@ -31526,7 +31531,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>274</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -31546,7 +31551,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -31656,22 +31661,22 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD98" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE98" t="inlineStr">
@@ -31706,22 +31711,22 @@
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AL98" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -31791,12 +31796,12 @@
       </c>
       <c r="BN98" t="inlineStr">
         <is>
-          <t>2026-06-08 18:15:58</t>
+          <t>2026-06-26 12:32:12</t>
         </is>
       </c>
       <c r="BO98" t="inlineStr">
         <is>
-          <t>2026-06-08 18:15:58</t>
+          <t>2026-06-26 12:32:12</t>
         </is>
       </c>
       <c r="BP98" t="inlineStr">
@@ -31806,7 +31811,7 @@
       </c>
       <c r="BQ98" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭博外环西路杭州奥体博览城</t>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BR98" t="inlineStr">
@@ -31826,17 +31831,17 @@
       </c>
       <c r="BU98" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/0a2c7b14a34d43d49040a6e7b4ebe517.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/2024e1ac542c4e9f93d7e4a68c21b378.mp3</t>
         </is>
       </c>
       <c r="BV98" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 分 31 秒 </t>
+          <t xml:space="preserve">2 分 20 秒 </t>
         </is>
       </c>
       <c r="BW98" t="inlineStr">
         <is>
-          <t>2026-06-08 18:12:24</t>
+          <t>2026-06-26 12:29:50</t>
         </is>
       </c>
       <c r="BX98" t="inlineStr">
@@ -31863,7 +31868,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>273</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -32003,12 +32008,12 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD99" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE99" t="inlineStr">
@@ -32043,22 +32048,22 @@
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AL99" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -32128,12 +32133,12 @@
       </c>
       <c r="BN99" t="inlineStr">
         <is>
-          <t>2026-06-08 17:38:29</t>
+          <t>2026-06-26 12:12:27</t>
         </is>
       </c>
       <c r="BO99" t="inlineStr">
         <is>
-          <t>2026-06-08 17:38:29</t>
+          <t>2026-06-26 12:12:27</t>
         </is>
       </c>
       <c r="BP99" t="inlineStr">
@@ -32143,7 +32148,7 @@
       </c>
       <c r="BQ99" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道Pet haven哈文宠物生活馆杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BR99" t="inlineStr">
@@ -32163,17 +32168,17 @@
       </c>
       <c r="BU99" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/c4a779b692b54623bdc699a31d4f5844.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/9464e89bd4a84c9589fab337e4b92669.mp3</t>
         </is>
       </c>
       <c r="BV99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 </t>
+          <t xml:space="preserve">2 分 41 秒 </t>
         </is>
       </c>
       <c r="BW99" t="inlineStr">
         <is>
-          <t>2026-06-08 17:36:27</t>
+          <t>2026-06-26 12:09:43</t>
         </is>
       </c>
       <c r="BX99" t="inlineStr">
@@ -32200,7 +32205,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>272</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -32210,7 +32215,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>住宿团队</t>
+          <t>散客</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -32250,7 +32255,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -32330,22 +32335,22 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD100" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE100" t="inlineStr">
@@ -32380,22 +32385,22 @@
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AL100" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -32440,12 +32445,12 @@
       </c>
       <c r="BE100" t="inlineStr">
         <is>
-          <t>比较满意</t>
+          <t>非常满意</t>
         </is>
       </c>
       <c r="BF100" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BG100" t="inlineStr">
@@ -32465,12 +32470,12 @@
       </c>
       <c r="BN100" t="inlineStr">
         <is>
-          <t>2026-06-08 16:39:13</t>
+          <t>2026-06-22 12:15:24</t>
         </is>
       </c>
       <c r="BO100" t="inlineStr">
         <is>
-          <t>2026-06-08 16:39:13</t>
+          <t>2026-06-22 12:15:24</t>
         </is>
       </c>
       <c r="BP100" t="inlineStr">
@@ -32480,7 +32485,7 @@
       </c>
       <c r="BQ100" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BR100" t="inlineStr">
@@ -32500,17 +32505,17 @@
       </c>
       <c r="BU100" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/08bfbac963fd4beaa64637cc8e470e51.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/ca9cf170544e47eeb7d7e898a46017d0.mp3</t>
         </is>
       </c>
       <c r="BV100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 34 秒 </t>
+          <t xml:space="preserve">2 分 56 秒 </t>
         </is>
       </c>
       <c r="BW100" t="inlineStr">
         <is>
-          <t>2026-06-08 16:36:36</t>
+          <t>2026-06-22 12:12:26</t>
         </is>
       </c>
       <c r="BX100" t="inlineStr">
@@ -32537,7 +32542,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>271</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -32557,12 +32562,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>36-45岁</t>
+          <t>46-55岁</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -32677,12 +32682,12 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD101" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE101" t="inlineStr">
@@ -32802,12 +32807,12 @@
       </c>
       <c r="BN101" t="inlineStr">
         <is>
-          <t>2026-06-08 16:29:35</t>
+          <t>2026-06-11 10:51:53</t>
         </is>
       </c>
       <c r="BO101" t="inlineStr">
         <is>
-          <t>2026-06-08 16:29:35</t>
+          <t>2026-06-11 10:51:53</t>
         </is>
       </c>
       <c r="BP101" t="inlineStr">
@@ -32817,7 +32822,7 @@
       </c>
       <c r="BQ101" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路万象世界中心</t>
         </is>
       </c>
       <c r="BR101" t="inlineStr">
@@ -32837,17 +32842,17 @@
       </c>
       <c r="BU101" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/35d3b3b5f493491192d33585c8d38787.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/31db1e02827040b5a6127c3c3c7a0048.mp3</t>
         </is>
       </c>
       <c r="BV101" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 分 3 秒 </t>
+          <t xml:space="preserve">2 分 56 秒 </t>
         </is>
       </c>
       <c r="BW101" t="inlineStr">
         <is>
-          <t>2026-06-08 16:26:29</t>
+          <t>2026-06-11 10:48:54</t>
         </is>
       </c>
       <c r="BX101" t="inlineStr">
@@ -32874,7 +32879,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>270</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -33004,22 +33009,22 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr">
@@ -33139,12 +33144,12 @@
       </c>
       <c r="BN102" t="inlineStr">
         <is>
-          <t>2026-06-08 15:02:02</t>
+          <t>2026-06-09 13:18:18</t>
         </is>
       </c>
       <c r="BO102" t="inlineStr">
         <is>
-          <t>2026-06-08 15:02:02</t>
+          <t>2026-06-09 13:18:18</t>
         </is>
       </c>
       <c r="BP102" t="inlineStr">
@@ -33154,7 +33159,7 @@
       </c>
       <c r="BQ102" t="inlineStr">
         <is>
-          <t>浙江省杭州市萧山区盈丰街道滨盛路万象世界中心</t>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
         </is>
       </c>
       <c r="BR102" t="inlineStr">
@@ -33174,17 +33179,17 @@
       </c>
       <c r="BU102" t="inlineStr">
         <is>
-          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/19f962c14c834f8fbdfcecafc28f5bcc.mp3</t>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/c848f3130ffa4aa7b70c43559a8851a1.mp3</t>
         </is>
       </c>
       <c r="BV102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 分 31 秒 </t>
+          <t xml:space="preserve">3 分 16 秒 </t>
         </is>
       </c>
       <c r="BW102" t="inlineStr">
         <is>
-          <t>2026-06-08 14:59:29</t>
+          <t>2026-06-09 13:14:59</t>
         </is>
       </c>
       <c r="BX102" t="inlineStr">
@@ -33211,335 +33216,4379 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>住宿团队</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BE103" t="inlineStr">
+        <is>
+          <t>非常满意</t>
+        </is>
+      </c>
+      <c r="BF103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG103" t="inlineStr">
+        <is>
+          <t>达到预期</t>
+        </is>
+      </c>
+      <c r="BH103" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI103" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BN103" t="inlineStr">
+        <is>
+          <t>2026-06-09 13:01:20</t>
+        </is>
+      </c>
+      <c r="BO103" t="inlineStr">
+        <is>
+          <t>2026-06-09 13:01:20</t>
+        </is>
+      </c>
+      <c r="BP103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BQ103" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道AFTERWORK健身(奥体AT中心店)杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BR103" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BS103" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BT103" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BU103" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/1337bdfe227749f48c0a36b44f66aaf5.mp3</t>
+        </is>
+      </c>
+      <c r="BV103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 分 3 秒 </t>
+        </is>
+      </c>
+      <c r="BW103" t="inlineStr">
+        <is>
+          <t>2026-06-09 12:58:14</t>
+        </is>
+      </c>
+      <c r="BX103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ103" t="inlineStr">
+        <is>
+          <t>0,286,289,302</t>
+        </is>
+      </c>
+      <c r="CA103" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>住宿团队</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AN104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BE104" t="inlineStr">
+        <is>
+          <t>比较满意</t>
+        </is>
+      </c>
+      <c r="BF104" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BG104" t="inlineStr">
+        <is>
+          <t>达到预期</t>
+        </is>
+      </c>
+      <c r="BH104" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI104" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BN104" t="inlineStr">
+        <is>
+          <t>2026-06-09 12:30:56</t>
+        </is>
+      </c>
+      <c r="BO104" t="inlineStr">
+        <is>
+          <t>2026-06-09 12:30:56</t>
+        </is>
+      </c>
+      <c r="BP104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BQ104" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BR104" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BS104" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BT104" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BU104" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/206b60b4daf54388840bd2a6c7a75e1a.mp3</t>
+        </is>
+      </c>
+      <c r="BV104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 分 28 秒 </t>
+        </is>
+      </c>
+      <c r="BW104" t="inlineStr">
+        <is>
+          <t>2026-06-09 12:27:25</t>
+        </is>
+      </c>
+      <c r="BX104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ104" t="inlineStr">
+        <is>
+          <t>0,286,289,302</t>
+        </is>
+      </c>
+      <c r="CA104" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>住宿团队</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BE105" t="inlineStr">
+        <is>
+          <t>非常满意</t>
+        </is>
+      </c>
+      <c r="BF105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG105" t="inlineStr">
+        <is>
+          <t>达到预期</t>
+        </is>
+      </c>
+      <c r="BH105" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI105" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BN105" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:44:30</t>
+        </is>
+      </c>
+      <c r="BO105" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:44:30</t>
+        </is>
+      </c>
+      <c r="BP105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BQ105" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BR105" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BS105" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BT105" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BU105" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/af0b874dfb9f4f40acee55aaeffa001c.mp3</t>
+        </is>
+      </c>
+      <c r="BV105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 分 24 秒 </t>
+        </is>
+      </c>
+      <c r="BW105" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:41:03</t>
+        </is>
+      </c>
+      <c r="BX105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ105" t="inlineStr">
+        <is>
+          <t>0,286,289,302</t>
+        </is>
+      </c>
+      <c r="CA105" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>住宿团队</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>26-35岁</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BE106" t="inlineStr">
+        <is>
+          <t>非常满意</t>
+        </is>
+      </c>
+      <c r="BF106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG106" t="inlineStr">
+        <is>
+          <t>达到预期</t>
+        </is>
+      </c>
+      <c r="BH106" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI106" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BN106" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:12:30</t>
+        </is>
+      </c>
+      <c r="BO106" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:12:30</t>
+        </is>
+      </c>
+      <c r="BP106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BQ106" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BR106" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BS106" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BT106" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BU106" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/539f67c7394847f38e4ed7a904bbd915.mp3</t>
+        </is>
+      </c>
+      <c r="BV106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 分 22 秒 </t>
+        </is>
+      </c>
+      <c r="BW106" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:10:05</t>
+        </is>
+      </c>
+      <c r="BX106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ106" t="inlineStr">
+        <is>
+          <t>0,286,289,302</t>
+        </is>
+      </c>
+      <c r="CA106" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>住宿团队</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AV107" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BB107" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BE107" t="inlineStr">
+        <is>
+          <t>非常满意</t>
+        </is>
+      </c>
+      <c r="BF107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG107" t="inlineStr">
+        <is>
+          <t>达到预期</t>
+        </is>
+      </c>
+      <c r="BH107" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI107" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BN107" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:03:03</t>
+        </is>
+      </c>
+      <c r="BO107" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:03:03</t>
+        </is>
+      </c>
+      <c r="BP107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BQ107" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BR107" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BS107" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BT107" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BU107" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/1635becd5ed443398dea66d96928f274.mp3</t>
+        </is>
+      </c>
+      <c r="BV107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 分 9 秒 </t>
+        </is>
+      </c>
+      <c r="BW107" t="inlineStr">
+        <is>
+          <t>2026-06-09 11:00:51</t>
+        </is>
+      </c>
+      <c r="BX107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ107" t="inlineStr">
+        <is>
+          <t>0,286,289,302</t>
+        </is>
+      </c>
+      <c r="CA107" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>住宿团队</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AP108" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AV108" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BB108" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BE108" t="inlineStr">
+        <is>
+          <t>非常满意</t>
+        </is>
+      </c>
+      <c r="BF108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG108" t="inlineStr">
+        <is>
+          <t>达到预期</t>
+        </is>
+      </c>
+      <c r="BH108" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI108" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BN108" t="inlineStr">
+        <is>
+          <t>2026-06-09 10:55:08</t>
+        </is>
+      </c>
+      <c r="BO108" t="inlineStr">
+        <is>
+          <t>2026-06-09 10:55:08</t>
+        </is>
+      </c>
+      <c r="BP108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BQ108" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BR108" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BS108" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BT108" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BU108" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/a4dd0b1c286a42f9ada06a7fc39b2920.mp3</t>
+        </is>
+      </c>
+      <c r="BV108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 分 58 秒 </t>
+        </is>
+      </c>
+      <c r="BW108" t="inlineStr">
+        <is>
+          <t>2026-06-09 10:53:07</t>
+        </is>
+      </c>
+      <c r="BX108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ108" t="inlineStr">
+        <is>
+          <t>0,286,289,302</t>
+        </is>
+      </c>
+      <c r="CA108" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>住宿团队</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>46-55岁</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AP109" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AV109" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BB109" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BE109" t="inlineStr">
+        <is>
+          <t>非常满意</t>
+        </is>
+      </c>
+      <c r="BF109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG109" t="inlineStr">
+        <is>
+          <t>达到预期</t>
+        </is>
+      </c>
+      <c r="BH109" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI109" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BN109" t="inlineStr">
+        <is>
+          <t>2026-06-08 18:30:21</t>
+        </is>
+      </c>
+      <c r="BO109" t="inlineStr">
+        <is>
+          <t>2026-06-08 18:30:21</t>
+        </is>
+      </c>
+      <c r="BP109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BQ109" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道XDS喜德盛自行车(杭州形象店)杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BR109" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BS109" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BT109" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BU109" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/fc77f000748948e2b27937bcfb5dd8fa.mp3</t>
+        </is>
+      </c>
+      <c r="BV109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 分 2 秒 </t>
+        </is>
+      </c>
+      <c r="BW109" t="inlineStr">
+        <is>
+          <t>2026-06-08 18:28:17</t>
+        </is>
+      </c>
+      <c r="BX109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ109" t="inlineStr">
+        <is>
+          <t>0,286,289,302</t>
+        </is>
+      </c>
+      <c r="CA109" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>住宿团队</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BB110" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BE110" t="inlineStr">
+        <is>
+          <t>非常满意</t>
+        </is>
+      </c>
+      <c r="BF110" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG110" t="inlineStr">
+        <is>
+          <t>达到预期</t>
+        </is>
+      </c>
+      <c r="BH110" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI110" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BN110" t="inlineStr">
+        <is>
+          <t>2026-06-08 18:15:58</t>
+        </is>
+      </c>
+      <c r="BO110" t="inlineStr">
+        <is>
+          <t>2026-06-08 18:15:58</t>
+        </is>
+      </c>
+      <c r="BP110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BQ110" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道杭博外环西路杭州奥体博览城</t>
+        </is>
+      </c>
+      <c r="BR110" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BS110" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BT110" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BU110" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/0a2c7b14a34d43d49040a6e7b4ebe517.mp3</t>
+        </is>
+      </c>
+      <c r="BV110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 分 31 秒 </t>
+        </is>
+      </c>
+      <c r="BW110" t="inlineStr">
+        <is>
+          <t>2026-06-08 18:12:24</t>
+        </is>
+      </c>
+      <c r="BX110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ110" t="inlineStr">
+        <is>
+          <t>0,286,289,302</t>
+        </is>
+      </c>
+      <c r="CA110" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>住宿团队</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AP111" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AV111" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BB111" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BE111" t="inlineStr">
+        <is>
+          <t>非常满意</t>
+        </is>
+      </c>
+      <c r="BF111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG111" t="inlineStr">
+        <is>
+          <t>达到预期</t>
+        </is>
+      </c>
+      <c r="BH111" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI111" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BN111" t="inlineStr">
+        <is>
+          <t>2026-06-08 17:38:29</t>
+        </is>
+      </c>
+      <c r="BO111" t="inlineStr">
+        <is>
+          <t>2026-06-08 17:38:29</t>
+        </is>
+      </c>
+      <c r="BP111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BQ111" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BR111" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BS111" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BT111" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BU111" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/c4a779b692b54623bdc699a31d4f5844.mp3</t>
+        </is>
+      </c>
+      <c r="BV111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 分 </t>
+        </is>
+      </c>
+      <c r="BW111" t="inlineStr">
+        <is>
+          <t>2026-06-08 17:36:27</t>
+        </is>
+      </c>
+      <c r="BX111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ111" t="inlineStr">
+        <is>
+          <t>0,286,289,302</t>
+        </is>
+      </c>
+      <c r="CA111" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>住宿团队</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AP112" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AV112" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BB112" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BE112" t="inlineStr">
+        <is>
+          <t>比较满意</t>
+        </is>
+      </c>
+      <c r="BF112" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BG112" t="inlineStr">
+        <is>
+          <t>达到预期</t>
+        </is>
+      </c>
+      <c r="BH112" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI112" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BN112" t="inlineStr">
+        <is>
+          <t>2026-06-08 16:39:13</t>
+        </is>
+      </c>
+      <c r="BO112" t="inlineStr">
+        <is>
+          <t>2026-06-08 16:39:13</t>
+        </is>
+      </c>
+      <c r="BP112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BQ112" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道杭州奥体博览城杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BR112" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BS112" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BT112" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BU112" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/08bfbac963fd4beaa64637cc8e470e51.mp3</t>
+        </is>
+      </c>
+      <c r="BV112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 分 34 秒 </t>
+        </is>
+      </c>
+      <c r="BW112" t="inlineStr">
+        <is>
+          <t>2026-06-08 16:36:36</t>
+        </is>
+      </c>
+      <c r="BX112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ112" t="inlineStr">
+        <is>
+          <t>0,286,289,302</t>
+        </is>
+      </c>
+      <c r="CA112" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>住宿团队</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AP113" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AV113" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BB113" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BE113" t="inlineStr">
+        <is>
+          <t>非常满意</t>
+        </is>
+      </c>
+      <c r="BF113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG113" t="inlineStr">
+        <is>
+          <t>达到预期</t>
+        </is>
+      </c>
+      <c r="BH113" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI113" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BN113" t="inlineStr">
+        <is>
+          <t>2026-06-08 16:29:35</t>
+        </is>
+      </c>
+      <c r="BO113" t="inlineStr">
+        <is>
+          <t>2026-06-08 16:29:35</t>
+        </is>
+      </c>
+      <c r="BP113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BQ113" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道FOR给予电音教育(杭州奥体AT天地)杭州奥体AT中心体育馆</t>
+        </is>
+      </c>
+      <c r="BR113" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BS113" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BT113" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BU113" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/35d3b3b5f493491192d33585c8d38787.mp3</t>
+        </is>
+      </c>
+      <c r="BV113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 分 3 秒 </t>
+        </is>
+      </c>
+      <c r="BW113" t="inlineStr">
+        <is>
+          <t>2026-06-08 16:26:29</t>
+        </is>
+      </c>
+      <c r="BX113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ113" t="inlineStr">
+        <is>
+          <t>0,286,289,302</t>
+        </is>
+      </c>
+      <c r="CA113" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>待提交审核</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>住宿团队</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>首次</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>36-45岁</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AP114" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AV114" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BE114" t="inlineStr">
+        <is>
+          <t>非常满意</t>
+        </is>
+      </c>
+      <c r="BF114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG114" t="inlineStr">
+        <is>
+          <t>达到预期</t>
+        </is>
+      </c>
+      <c r="BH114" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="BI114" t="inlineStr">
+        <is>
+          <t>会推荐</t>
+        </is>
+      </c>
+      <c r="BN114" t="inlineStr">
+        <is>
+          <t>2026-06-08 15:02:02</t>
+        </is>
+      </c>
+      <c r="BO114" t="inlineStr">
+        <is>
+          <t>2026-06-08 15:02:02</t>
+        </is>
+      </c>
+      <c r="BP114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BQ114" t="inlineStr">
+        <is>
+          <t>浙江省杭州市萧山区盈丰街道滨盛路万象世界中心</t>
+        </is>
+      </c>
+      <c r="BR114" t="inlineStr">
+        <is>
+          <t>杭博访问员2</t>
+        </is>
+      </c>
+      <c r="BS114" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="BT114" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BU114" t="inlineStr">
+        <is>
+          <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/19f962c14c834f8fbdfcecafc28f5bcc.mp3</t>
+        </is>
+      </c>
+      <c r="BV114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 分 31 秒 </t>
+        </is>
+      </c>
+      <c r="BW114" t="inlineStr">
+        <is>
+          <t>2026-06-08 14:59:29</t>
+        </is>
+      </c>
+      <c r="BX114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ114" t="inlineStr">
+        <is>
+          <t>0,286,289,302</t>
+        </is>
+      </c>
+      <c r="CA114" t="inlineStr">
+        <is>
+          <t>一期</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>待提交审核</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>住宿团队</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D115" t="inlineStr">
         <is>
           <t>首次</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E115" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F115" t="inlineStr">
         <is>
           <t>36-45岁</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="T103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="W103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="X103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="AD103" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="AE103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AF103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AG103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AL103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AP103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AQ103" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>不涉及</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr">
-        <is>
-          <t>不知道</t>
-        </is>
-      </c>
-      <c r="AV103" t="inlineStr">
-        <is>
-          <t>不知道</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr">
-        <is>
-          <t>不知道</t>
-        </is>
-      </c>
-      <c r="BB103" t="inlineStr">
-        <is>
-          <t>不知道</t>
-        </is>
-      </c>
-      <c r="BE103" t="inlineStr">
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AL115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AN115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AP115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AV115" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BB115" t="inlineStr">
+        <is>
+          <t>不知道</t>
+        </is>
+      </c>
+      <c r="BE115" t="inlineStr">
         <is>
           <t>非常满意</t>
         </is>
       </c>
-      <c r="BF103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BG103" t="inlineStr">
+      <c r="BF115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG115" t="inlineStr">
         <is>
           <t>达到预期</t>
         </is>
       </c>
-      <c r="BH103" t="inlineStr">
+      <c r="BH115" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="BI103" t="inlineStr">
+      <c r="BI115" t="inlineStr">
         <is>
           <t>会推荐</t>
         </is>
       </c>
-      <c r="BN103" t="inlineStr">
+      <c r="BN115" t="inlineStr">
         <is>
           <t>2026-06-08 14:51:31</t>
         </is>
       </c>
-      <c r="BO103" t="inlineStr">
+      <c r="BO115" t="inlineStr">
         <is>
           <t>2026-06-08 14:51:31</t>
         </is>
       </c>
-      <c r="BP103" t="inlineStr">
+      <c r="BP115" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BQ103" t="inlineStr">
+      <c r="BQ115" t="inlineStr">
         <is>
           <t>浙江省杭州市萧山区盈丰街道滨盛路杭州奥体博览城</t>
         </is>
       </c>
-      <c r="BR103" t="inlineStr">
+      <c r="BR115" t="inlineStr">
         <is>
           <t>杭博访问员2</t>
         </is>
       </c>
-      <c r="BS103" t="inlineStr">
+      <c r="BS115" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="BT103" t="inlineStr">
+      <c r="BT115" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="BU103" t="inlineStr">
+      <c r="BU115" t="inlineStr">
         <is>
           <t>https://file.fieldzx.com/562536bef2e6db873811ade7440ce182/82aa50da7568420d86d339c23d6a94a9.mp3</t>
         </is>
       </c>
-      <c r="BV103" t="inlineStr">
+      <c r="BV115" t="inlineStr">
         <is>
           <t xml:space="preserve">2 分 35 秒 </t>
         </is>
       </c>
-      <c r="BW103" t="inlineStr">
+      <c r="BW115" t="inlineStr">
         <is>
           <t>2026-06-08 14:48:52</t>
         </is>
       </c>
-      <c r="BX103" t="inlineStr">
+      <c r="BX115" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BY103" t="inlineStr">
+      <c r="BY115" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BZ103" t="inlineStr">
+      <c r="BZ115" t="inlineStr">
         <is>
           <t>0,286,289,302</t>
         </is>
       </c>
-      <c r="CA103" t="inlineStr">
+      <c r="CA115" t="inlineStr">
         <is>
           <t>一期</t>
         </is>
